--- a/BOM/POGO_Tester_Rev1 - BOM.xlsx
+++ b/BOM/POGO_Tester_Rev1 - BOM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PCB Projects\POGO_Tester_Rev1\Project Outputs for POGO_Tester_Rev1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PCB Projects\POGO_Tester_Rev1\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE7E421F-1778-4B45-927D-4EAC39BBF530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A20463C5-A929-46EC-98FF-DC788CF410E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39855" yWindow="2715" windowWidth="28800" windowHeight="15345" xr2:uid="{A688E626-0F3A-4B19-AF70-3A82F7CFB395}"/>
+    <workbookView xWindow="945" yWindow="-15075" windowWidth="21600" windowHeight="11295" xr2:uid="{A688E626-0F3A-4B19-AF70-3A82F7CFB395}"/>
   </bookViews>
   <sheets>
     <sheet name="POGO_Tester_Rev1" sheetId="1" r:id="rId1"/>
@@ -96,7 +96,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -106,6 +106,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD3D3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -137,12 +143,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -502,20 +511,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="6">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -536,18 +545,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1">
+      <c r="C4" s="6"/>
+      <c r="D4" s="6">
         <v>10</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="5" t="s">
         <v>8</v>
       </c>
     </row>
